--- a/vignettes/vignette-2/donor_selection.xlsx
+++ b/vignettes/vignette-2/donor_selection.xlsx
@@ -522,32 +522,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1274_2015</t>
+          <t>218_2016</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1274</v>
+        <v>218</v>
       </c>
       <c r="D3" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="E3" t="n">
-        <v>446.119</v>
+        <v>570.85</v>
       </c>
       <c r="F3" t="n">
-        <v>23.366</v>
+        <v>56.55</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05237615972419914</v>
+        <v>0.09906280108609966</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4890486097902354</v>
+        <v>0.4907903107262704</v>
       </c>
       <c r="I3" t="n">
-        <v>0.967766</v>
+        <v>0.970059</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.376387</v>
+        <v>-0.129846</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>

--- a/vignettes/vignette-2/donor_selection.xlsx
+++ b/vignettes/vignette-2/donor_selection.xlsx
@@ -522,32 +522,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>218_2016</t>
+          <t>1274_2021</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>218</v>
+        <v>1274</v>
       </c>
       <c r="D3" t="n">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="E3" t="n">
-        <v>570.85</v>
+        <v>798.8118518518518</v>
       </c>
       <c r="F3" t="n">
-        <v>56.55</v>
+        <v>53.8111111111111</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09906280108609966</v>
+        <v>0.06736393680985463</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4907903107262704</v>
+        <v>0.5149713238063</v>
       </c>
       <c r="I3" t="n">
-        <v>0.970059</v>
+        <v>0.970171</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.129846</v>
+        <v>0.206153</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
